--- a/opengever/bundle/tests/assets/os_migration/os_test_move.xlsx
+++ b/opengever/bundle/tests/assets/os_migration/os_test_move.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Work/development/opengever.core/opengever/bundle/tests/assets/os_migration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52225958-57A6-C542-8FD0-C9908A3D79E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D036260D-F84D-AA45-BFF6-A7CDD6FF24A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2260" yWindow="5460" windowWidth="25920" windowHeight="10340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14228,6 +14228,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <oc_termin_lookup_helper xmlns="82675a1d-2274-46ff-95b6-7e628f04e7b8" xsi:nil="true"/>
@@ -14237,15 +14246,6 @@
     <oc_traktandum_lookup_helper xmlns="82675a1d-2274-46ff-95b6-7e628f04e7b8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14268,6 +14268,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5B73656-B986-42B5-A6F0-2CB7C4F8F507}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63B1394A-812F-4D99-A0FC-B41B7F31C120}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14276,12 +14284,4 @@
     <ds:schemaRef ds:uri="96CA5592-7E49-4C69-936A-77E0F19F316B"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5B73656-B986-42B5-A6F0-2CB7C4F8F507}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>